--- a/data/trans_orig/P42C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Provincia-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2012 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53670</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40760</t>
+          <t>41826</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68463</t>
+          <t>69001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>53670</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>40760</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>68463</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>29,15%</t>
+          <t>29,38%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181206</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>193050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166413</t>
+          <t>165875</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194116</t>
+          <t>193050</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>181206</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>166413</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>194116</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>70,85%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
+          <t>82,19%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234876</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>234876</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>234876</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>234876</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98357</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118982</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81958</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118016</t>
+          <t>118982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>98357</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>81958</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>118016</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>22,64%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>18,87%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>27,17%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>309</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>336077</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>315452</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>352977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>316418</t>
+          <t>315452</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352476</t>
+          <t>352977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>336077</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>316418</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>352476</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>77,36%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>72,83%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>81,13%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>434434</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>434434</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>434434</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>52</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57655</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72459</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43775</t>
+          <t>44516</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70586</t>
+          <t>72459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>57655</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>43775</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>70586</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>21,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>26,36%</t>
+          <t>27,06%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>210132</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195328</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197201</t>
+          <t>195328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224012</t>
+          <t>223271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>210132</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>197201</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>224012</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>78,47%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>73,64%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
+          <t>83,38%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267787</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267787</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>267787</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>267787</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>267787</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>86922</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>70688</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102537</t>
+          <t>104369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>86922</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>70688</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>102537</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>30,09%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>35,5%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>194</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>201947</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>186332</t>
+          <t>184500</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>218181</t>
+          <t>215885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>186332</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>218181</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>69,91%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>64,5%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>276</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288869</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288869</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288869</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>288869</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>288869</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>288869</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2094,37 +1614,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37386</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,47 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>49433</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>37386</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>61010</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>29,18%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>36,02%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -2207,37 +1692,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>106033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>130867</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108384</t>
+          <t>106033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132008</t>
+          <t>130867</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,47 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>119961</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>108384</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>132008</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>70,82%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>63,98%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>77,93%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -2320,37 +1770,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>163</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169394</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169394</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2384,41 +1834,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>169394</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>169394</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>169394</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2437,37 +1852,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>44953</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32832</t>
+          <t>33142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>59283</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,47 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>44953</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>32832</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>57945</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>15,29%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -2550,37 +1930,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169839</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>155509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>181650</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>156847</t>
+          <t>155509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181960</t>
+          <t>181650</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,47 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>169839</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>156847</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>181960</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>84,71%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2008,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214792</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214792</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214792</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2727,41 +2072,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>214792</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>214792</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>214792</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2780,37 +2090,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135901</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114717</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157733</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>115629</t>
+          <t>114717</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158821</t>
+          <t>157733</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,47 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>135901</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>115629</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>158821</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>24,3%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>20,67%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>28,39%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -2893,37 +2168,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>423434</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>401602</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400514</t>
+          <t>401602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>443706</t>
+          <t>444618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,47 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>423434</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>400514</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>443706</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>75,7%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>71,61%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>79,33%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -3006,37 +2246,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>507</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559335</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559335</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>559335</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3070,41 +2310,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>559335</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>559335</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>559335</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3123,37 +2328,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>128784</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>150557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +2373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>109014</t>
+          <t>108737</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>149600</t>
+          <t>150557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,47 +2388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>128784</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>109014</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>149600</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>19,11%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>26,22%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -3236,37 +2406,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>410</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>441762</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>419989</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>461809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +2451,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>420946</t>
+          <t>419989</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>461532</t>
+          <t>461809</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,47 +2466,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>441762</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>420946</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>461532</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>77,43%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>73,78%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>80,89%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -3349,37 +2484,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570546</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570546</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>570546</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3413,41 +2548,6 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>570546</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>570546</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>570546</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3466,37 +2566,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>655675</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>601929</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>701351</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +2611,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>611083</t>
+          <t>601929</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>705108</t>
+          <t>701351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,47 +2626,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>655675</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>611083</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>705108</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>25,73%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -3579,37 +2644,37 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1936</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2084359</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2038683</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2138105</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +2689,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2034926</t>
+          <t>2038683</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2128951</t>
+          <t>2138105</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,47 +2704,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2084359</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2034926</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2128951</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>76,07%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>74,27%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>77,7%</t>
+          <t>78,03%</t>
         </is>
       </c>
     </row>
@@ -3692,37 +2722,37 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2740034</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2740034</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2740034</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3756,41 +2786,6 @@
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2524</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2740034</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>2740034</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2740034</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3804,7 +2799,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -3814,7 +2809,6 @@
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -3829,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3848,25 +2842,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2016 (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +2864,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3886,17 +2873,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3967,41 +2943,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -4024,13 +2965,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4045,37 +2979,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +3024,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38500</t>
+          <t>39600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65181</t>
+          <t>64124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,47 +3039,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>50722</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>38500</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>65181</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>16,92%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>28,64%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -4158,37 +3057,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176870</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +3102,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>162411</t>
+          <t>163468</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189092</t>
+          <t>187992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,47 +3117,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>176870</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>162411</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>189092</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>71,36%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>83,08%</t>
+          <t>82,6%</t>
         </is>
       </c>
     </row>
@@ -4271,37 +3135,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>218</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227592</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227592</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>227592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4335,41 +3199,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>227592</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>227592</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>227592</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4388,37 +3217,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59504</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +3262,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46274</t>
+          <t>46325</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74778</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,47 +3277,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>59504</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>46274</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>74778</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>14,9%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>11,58%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -4501,37 +3295,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>318</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>339980</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +3340,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324706</t>
+          <t>325375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353210</t>
+          <t>353159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,47 +3355,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>339980</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>324706</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>353210</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>85,1%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>81,28%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -4614,37 +3373,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399484</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>399484</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4678,41 +3437,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>399484</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>399484</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>399484</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4731,37 +3455,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +3500,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8900</t>
+          <t>9661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,47 +3515,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>15350</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>8900</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>23578</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>8,55%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -4844,37 +3533,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>260352</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>250151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>266041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +3578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>252124</t>
+          <t>250151</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266802</t>
+          <t>266041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,47 +3593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>260352</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>252124</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>266802</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>94,43%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>91,45%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -4957,37 +3611,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275702</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275702</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5021,41 +3675,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>275702</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>275702</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>275702</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5074,37 +3693,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +3738,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53349</t>
+          <t>50670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,47 +3753,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>38040</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>27054</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>53349</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -5187,37 +3771,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>247340</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>234710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>258651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +3816,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232031</t>
+          <t>234710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258326</t>
+          <t>258651</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,47 +3831,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>247340</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>232031</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>258326</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>86,67%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>81,31%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>90,52%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -5300,37 +3849,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>263</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285380</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5364,41 +3913,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>285380</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>285380</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>285380</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5417,37 +3931,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +3976,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,47 +3991,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>6221</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2633</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>12313</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5530,37 +4009,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162987</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156730</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>166549</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +4054,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156895</t>
+          <t>156730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166575</t>
+          <t>166549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,47 +4069,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>162987</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>156895</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>166575</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,32%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -5643,37 +4087,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>172</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5707,41 +4151,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>169208</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>169208</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>169208</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5760,37 +4169,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37313</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +4214,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27545</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49804</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,47 +4229,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>37313</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>27545</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>49804</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>13,29%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -5873,37 +4247,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>169955</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157199</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +4292,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157464</t>
+          <t>157199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179723</t>
+          <t>180265</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,47 +4307,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>169955</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>157464</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>179723</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>75,97%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>86,71%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -5986,37 +4325,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207268</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207268</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6050,41 +4389,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>207268</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>207268</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>207268</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6103,37 +4407,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>127274</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>108772</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +4452,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108366</t>
+          <t>108772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147521</t>
+          <t>148909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,47 +4467,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>127274</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>108366</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>147521</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>20,03%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -6216,37 +4485,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>389</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>413871</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392236</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>432373</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +4530,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>393624</t>
+          <t>392236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>432779</t>
+          <t>432373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,47 +4545,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>389</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>413871</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>393624</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>432779</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>76,48%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>72,74%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>79,97%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -6329,37 +4563,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>509</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541145</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541145</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>541145</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6393,41 +4627,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>541145</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>541145</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>541145</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6446,37 +4645,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95108</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>78186</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +4690,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75924</t>
+          <t>78186</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>115638</t>
+          <t>117650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,47 +4705,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>95108</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>75924</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>115638</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -6559,37 +4723,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>530</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>575867</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>553325</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>592789</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +4768,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>555337</t>
+          <t>553325</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>595051</t>
+          <t>592789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,47 +4783,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>575867</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>555337</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>595051</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -6672,37 +4801,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>670975</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>670975</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>670975</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6736,41 +4865,6 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>670975</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>670975</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>670975</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -6789,37 +4883,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>404</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429531</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>390425</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470981</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +4928,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>395628</t>
+          <t>390425</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>472258</t>
+          <t>470981</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,47 +4943,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>429531</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>395628</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>472258</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>14,25%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>17,01%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -6902,37 +4961,37 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2347223</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2305773</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2386329</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +5006,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2304496</t>
+          <t>2305773</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2381126</t>
+          <t>2386329</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,47 +5021,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2347223</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2304496</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2381126</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>82,99%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>85,75%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -7015,37 +5039,37 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2776754</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2776754</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2776754</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7079,41 +5103,6 @@
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2622</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2776754</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>2776754</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2776754</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7127,7 +5116,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -7137,7 +5126,6 @@
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
@@ -7152,7 +5140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7171,25 +5159,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +5181,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7209,17 +5190,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -7290,41 +5260,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -7347,13 +5282,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -7368,37 +5296,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +5341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44066</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,47 +5356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>33720</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>26559</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>44066</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>21,43%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -7481,37 +5374,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123611</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>114869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>131621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +5419,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113265</t>
+          <t>114869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130772</t>
+          <t>131621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,47 +5434,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>123611</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>113265</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>130772</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>78,57%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>71,99%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -7594,37 +5452,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157331</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>157331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7658,41 +5516,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>157331</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>157331</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>157331</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -7711,37 +5534,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90181</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>105832</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +5579,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>76626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107171</t>
+          <t>105832</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,47 +5594,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>90181</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>76382</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>107171</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>27,23%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -7824,37 +5612,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>342</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>241024</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254579</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +5657,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224034</t>
+          <t>225373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254823</t>
+          <t>254579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,47 +5672,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>241024</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>224034</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>254823</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>72,77%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>67,64%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
+          <t>76,86%</t>
         </is>
       </c>
     </row>
@@ -7937,37 +5690,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331205</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331205</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>331205</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8001,41 +5754,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>331205</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>331205</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>331205</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8054,37 +5772,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31000</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +5817,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23537</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>38981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,47 +5832,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>31000</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>23537</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>41075</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>17,26%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>22,87%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -8167,37 +5850,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148575</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156095</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +5895,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138500</t>
+          <t>140594</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156038</t>
+          <t>156095</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,47 +5910,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>148575</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>138500</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>156038</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>82,74%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>77,13%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>86,89%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -8280,37 +5928,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>296</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179575</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179575</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>179575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8344,41 +5992,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>179575</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>179575</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>179575</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8397,37 +6010,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +6055,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26385</t>
+          <t>24566</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76728</t>
+          <t>76512</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,47 +6070,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>52276</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>26385</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>76728</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -8510,37 +6088,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>274113</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +6133,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249661</t>
+          <t>249877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>300004</t>
+          <t>301823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,47 +6148,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>274113</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>249661</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>300004</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>83,98%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>76,49%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>91,92%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -8623,37 +6166,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>371</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326389</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326389</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>326389</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8687,41 +6230,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>326389</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>326389</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>326389</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -8740,37 +6248,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24352</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +6293,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31469</t>
+          <t>30994</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,47 +6308,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>24352</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>18737</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>31469</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,84%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>14,5%</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -8853,37 +6326,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>263</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104880</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>98238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>110384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +6371,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97763</t>
+          <t>98238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110495</t>
+          <t>110384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,47 +6386,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>104880</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>97763</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>110495</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>81,16%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>75,65%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>85,5%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -8966,37 +6404,37 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>317</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9030,41 +6468,6 @@
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>129232</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>129232</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>129232</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9083,37 +6486,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21625</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +6531,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15614</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,47 +6546,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>21625</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>15614</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>28742</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -9196,37 +6564,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>232</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115307</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>107357</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +6609,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108190</t>
+          <t>107357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121318</t>
+          <t>121541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,47 +6624,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>115307</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>108190</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>121318</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
+          <t>88,76%</t>
         </is>
       </c>
     </row>
@@ -9309,37 +6642,37 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136932</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136932</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136932</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9373,41 +6706,6 @@
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>136932</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>136932</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>136932</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9426,37 +6724,37 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>153629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +6769,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>154924</t>
+          <t>153629</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187866</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,47 +6784,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>170898</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>154924</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>187866</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>40,93%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>49,63%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -9539,37 +6802,37 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>328</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>207651</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>191545</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>224920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +6847,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>191545</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>223625</t>
+          <t>224920</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,47 +6862,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>207651</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>190683</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>223625</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>54,85%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>50,37%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>59,07%</t>
+          <t>59,42%</t>
         </is>
       </c>
     </row>
@@ -9652,37 +6880,37 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>574</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378549</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378549</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>378549</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9716,41 +6944,6 @@
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>378549</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>378549</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>378549</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -9769,37 +6962,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43286</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34633</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +7007,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32910</t>
+          <t>34633</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54286</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,47 +7022,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>43286</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>32910</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>54286</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>14,45%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -9882,37 +7040,37 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>524</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>332307</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320190</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +7085,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>321307</t>
+          <t>320190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>342683</t>
+          <t>340960</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,47 +7100,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>332307</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>321307</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>342683</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>88,48%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>85,55%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>91,24%</t>
+          <t>90,78%</t>
         </is>
       </c>
     </row>
@@ -9995,37 +7118,37 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>586</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375593</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375593</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>375593</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10059,41 +7182,6 @@
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>375593</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>375593</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>375593</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10112,37 +7200,37 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>711</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>467337</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403168</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>503641</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +7245,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>411727</t>
+          <t>403168</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>508802</t>
+          <t>503641</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,47 +7260,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>467337</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>411727</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>508802</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -10225,37 +7278,37 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1547468</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1511164</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1611637</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +7323,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1506003</t>
+          <t>1511164</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1603078</t>
+          <t>1611637</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,47 +7338,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1547468</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1506003</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1603078</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>74,75%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
+          <t>79,99%</t>
         </is>
       </c>
     </row>
@@ -10338,37 +7356,37 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2014805</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2014805</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2014805</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10402,41 +7420,6 @@
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>3179</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2014805</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>2014805</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2014805</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -10450,7 +7433,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
@@ -10460,7 +7443,6 @@
     <mergeCell ref="A28:A30"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>

--- a/data/trans_orig/P42C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Provincia-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>41037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>68848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>41037</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>68848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165875</t>
+          <t>166028</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193050</t>
+          <t>193839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>165875</t>
+          <t>166028</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>193050</t>
+          <t>193839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81457</t>
+          <t>80113</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118982</t>
+          <t>116000</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81457</t>
+          <t>80113</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118982</t>
+          <t>116000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>315452</t>
+          <t>318434</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>352977</t>
+          <t>354321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315452</t>
+          <t>318434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>352977</t>
+          <t>354321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44516</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>73464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44516</t>
+          <t>44758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72459</t>
+          <t>73464</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195328</t>
+          <t>194323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223271</t>
+          <t>223029</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195328</t>
+          <t>194323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>223271</t>
+          <t>223029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,29%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>72790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>104369</t>
+          <t>102996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>72790</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104369</t>
+          <t>102996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184500</t>
+          <t>185873</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>215885</t>
+          <t>216079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184500</t>
+          <t>185873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>215885</t>
+          <t>216079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63361</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>37555</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63361</t>
+          <t>61562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106033</t>
+          <t>107832</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130867</t>
+          <t>131839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106033</t>
+          <t>107832</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>130867</t>
+          <t>131839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33142</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59283</t>
+          <t>57735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1897,12 +1897,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33142</t>
+          <t>33362</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59283</t>
+          <t>57735</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>157057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181650</t>
+          <t>181430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>157057</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>181650</t>
+          <t>181430</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114717</t>
+          <t>115652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157733</t>
+          <t>158315</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>114717</t>
+          <t>115652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157733</t>
+          <t>158315</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>401602</t>
+          <t>401020</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>444618</t>
+          <t>443683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2193,12 +2193,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401602</t>
+          <t>401020</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>444618</t>
+          <t>443683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108737</t>
+          <t>108223</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>150557</t>
+          <t>151443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>108737</t>
+          <t>108223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>150557</t>
+          <t>151443</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>419989</t>
+          <t>419103</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>461809</t>
+          <t>462323</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>419989</t>
+          <t>419103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>461809</t>
+          <t>462323</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2466,12 +2466,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>601929</t>
+          <t>610767</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>701351</t>
+          <t>709432</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>601929</t>
+          <t>610767</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>701351</t>
+          <t>709432</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2038683</t>
+          <t>2030602</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2138105</t>
+          <t>2129267</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2669,12 +2669,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2038683</t>
+          <t>2030602</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2138105</t>
+          <t>2129267</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -2989,12 +2989,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39600</t>
+          <t>38323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64124</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3067,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163468</t>
+          <t>162950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187992</t>
+          <t>189269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>163468</t>
+          <t>162950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>187992</t>
+          <t>189269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46325</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46325</t>
+          <t>46267</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325375</t>
+          <t>323750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>353159</t>
+          <t>353217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>325375</t>
+          <t>323750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>353159</t>
+          <t>353217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3355,12 +3355,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9661</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25551</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>250151</t>
+          <t>251498</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>266041</t>
+          <t>266527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250151</t>
+          <t>251498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266041</t>
+          <t>266527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,67%</t>
         </is>
       </c>
     </row>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50670</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26729</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50670</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234710</t>
+          <t>233760</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258651</t>
+          <t>258708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234710</t>
+          <t>233760</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>258651</t>
+          <t>258708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3941,12 +3941,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>11874</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>156730</t>
+          <t>157334</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166549</t>
+          <t>166554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>156730</t>
+          <t>157334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>166549</t>
+          <t>166554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50069</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50069</t>
+          <t>48628</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157199</t>
+          <t>158640</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180265</t>
+          <t>179705</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157199</t>
+          <t>158640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>180265</t>
+          <t>179705</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>108772</t>
+          <t>109135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148909</t>
+          <t>148210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108772</t>
+          <t>109135</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148909</t>
+          <t>148210</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,39%</t>
         </is>
       </c>
     </row>
@@ -4495,12 +4495,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>392236</t>
+          <t>392935</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>432373</t>
+          <t>432010</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>392236</t>
+          <t>392935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>432373</t>
+          <t>432010</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,83%</t>
         </is>
       </c>
     </row>
@@ -4655,12 +4655,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78186</t>
+          <t>78039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>117650</t>
+          <t>115486</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78186</t>
+          <t>78039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117650</t>
+          <t>115486</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4733,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>553325</t>
+          <t>555489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>592789</t>
+          <t>592936</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>553325</t>
+          <t>555489</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>592789</t>
+          <t>592936</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>390425</t>
+          <t>393932</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>470981</t>
+          <t>471432</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>390425</t>
+          <t>393932</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>470981</t>
+          <t>471432</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,98%</t>
         </is>
       </c>
     </row>
@@ -4971,12 +4971,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2305773</t>
+          <t>2305322</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2386329</t>
+          <t>2382822</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2305773</t>
+          <t>2305322</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2386329</t>
+          <t>2382822</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -5301,32 +5301,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5336,32 +5336,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>33102</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -5379,32 +5379,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123611</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114869</t>
+          <t>131250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131621</t>
+          <t>147355</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5414,32 +5414,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>123611</t>
+          <t>140005</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114869</t>
+          <t>131250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131621</t>
+          <t>147355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -5457,17 +5457,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5492,17 +5492,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>157331</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5539,32 +5539,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>90181</t>
+          <t>94996</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76626</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>105832</t>
+          <t>111900</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5574,32 +5574,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90181</t>
+          <t>94996</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76626</t>
+          <t>80973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105832</t>
+          <t>111900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -5617,32 +5617,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>241024</t>
+          <t>252879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>225373</t>
+          <t>235975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254579</t>
+          <t>266902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5652,32 +5652,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>241024</t>
+          <t>252879</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225373</t>
+          <t>235975</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>254579</t>
+          <t>266902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -5695,17 +5695,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5730,17 +5730,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>331205</t>
+          <t>347875</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5777,32 +5777,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>39316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5812,32 +5812,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31000</t>
+          <t>31085</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38981</t>
+          <t>39316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -5855,32 +5855,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>148575</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140594</t>
+          <t>145068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156095</t>
+          <t>161346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5890,32 +5890,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>148575</t>
+          <t>153299</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140594</t>
+          <t>145068</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156095</t>
+          <t>161346</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,51%</t>
         </is>
       </c>
     </row>
@@ -5933,17 +5933,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>184384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>184384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>184384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5968,17 +5968,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>184384</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>184384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>184384</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6015,32 +6015,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>52276</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>48441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76512</t>
+          <t>71654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6050,32 +6050,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>52276</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24566</t>
+          <t>48441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76512</t>
+          <t>71654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>28,62%</t>
         </is>
       </c>
     </row>
@@ -6093,32 +6093,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>274113</t>
+          <t>192057</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249877</t>
+          <t>178702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>201915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6128,32 +6128,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>274113</t>
+          <t>192057</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249877</t>
+          <t>178702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>301823</t>
+          <t>201915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -6171,17 +6171,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>326389</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>326389</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>326389</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6206,17 +6206,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326389</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326389</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>326389</t>
+          <t>250356</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6253,32 +6253,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6288,32 +6288,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24352</t>
+          <t>26988</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>20836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -6331,32 +6331,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104880</t>
+          <t>112810</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98238</t>
+          <t>106011</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110384</t>
+          <t>118962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6366,32 +6366,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>104880</t>
+          <t>112810</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>98238</t>
+          <t>106011</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>110384</t>
+          <t>118962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -6409,17 +6409,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6444,17 +6444,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129232</t>
+          <t>139798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6491,32 +6491,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6526,32 +6526,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>23207</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>117204</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107357</t>
+          <t>110777</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>115307</t>
+          <t>117204</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>107357</t>
+          <t>110777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121541</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,21%</t>
         </is>
       </c>
     </row>
@@ -6647,17 +6647,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6682,17 +6682,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6729,32 +6729,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>170898</t>
+          <t>195796</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153629</t>
+          <t>176130</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187004</t>
+          <t>215176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6764,32 +6764,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>170898</t>
+          <t>195796</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>153629</t>
+          <t>176130</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187004</t>
+          <t>215176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -6807,32 +6807,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>207651</t>
+          <t>254077</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>191545</t>
+          <t>234697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224920</t>
+          <t>273743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6842,32 +6842,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>207651</t>
+          <t>254077</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>191545</t>
+          <t>234697</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>224920</t>
+          <t>273743</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>60,85%</t>
         </is>
       </c>
     </row>
@@ -6885,17 +6885,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>378549</t>
+          <t>449873</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>378549</t>
+          <t>449873</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>378549</t>
+          <t>449873</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6920,17 +6920,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>378549</t>
+          <t>449873</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>378549</t>
+          <t>449873</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>378549</t>
+          <t>449873</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6967,32 +6967,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>43286</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>34633</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55403</t>
+          <t>62430</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7002,32 +7002,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43286</t>
+          <t>49350</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34633</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55403</t>
+          <t>62430</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -7045,32 +7045,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>332307</t>
+          <t>375088</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>320190</t>
+          <t>362008</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>340960</t>
+          <t>386191</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7080,32 +7080,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>332307</t>
+          <t>375088</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>320190</t>
+          <t>362008</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>340960</t>
+          <t>386191</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,99%</t>
         </is>
       </c>
     </row>
@@ -7123,17 +7123,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>375593</t>
+          <t>424438</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>375593</t>
+          <t>424438</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>375593</t>
+          <t>424438</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7158,17 +7158,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>375593</t>
+          <t>424438</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>375593</t>
+          <t>424438</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>375593</t>
+          <t>424438</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7205,32 +7205,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>403168</t>
+          <t>477218</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>503641</t>
+          <t>548651</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7240,32 +7240,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>467337</t>
+          <t>512824</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>403168</t>
+          <t>477218</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>503641</t>
+          <t>548651</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -7283,32 +7283,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1547468</t>
+          <t>1597419</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1511164</t>
+          <t>1561592</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1611637</t>
+          <t>1633025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7318,32 +7318,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1547468</t>
+          <t>1597419</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1511164</t>
+          <t>1561592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1611637</t>
+          <t>1633025</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>77,39%</t>
         </is>
       </c>
     </row>
@@ -7361,17 +7361,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7396,17 +7396,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2014805</t>
+          <t>2110243</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
